--- a/data/trans_dic/IP38E_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente</t>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,97; 100,0</t>
+          <t>49,78; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77,93; 100,0</t>
+          <t>78,47; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,33; 100,0</t>
+          <t>63,03; 100,0</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,45; 100,0</t>
+          <t>66,4; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,98; 100,0</t>
+          <t>78,71; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,08; 98,19</t>
+          <t>82,25; 100,0</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,31; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,68; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,74; 97,51</t>
+          <t>85,57; 97,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,33; 94,19</t>
+          <t>74,39; 94,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,33; 95,23</t>
+          <t>84,07; 94,99</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,22; 93,4</t>
+          <t>73,45; 92,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,05; 94,89</t>
+          <t>82,08; 94,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,81; 92,55</t>
+          <t>81,04; 92,26</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,11; 86,58</t>
+          <t>69,17; 86,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,59; 94,15</t>
+          <t>79,22; 94,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77,46; 88,77</t>
+          <t>77,34; 88,54</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>79,89; 89,92</t>
+          <t>80,22; 89,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,36; 93,47</t>
+          <t>85,98; 93,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85,11; 90,84</t>
+          <t>84,99; 90,97</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que aporta más ingresos al hogar que trabaja actualmente (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>16166</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20991</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37157</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>9676; 19435</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17173; 21885</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26045; 41320</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13664</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15451</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29115</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10114; 15232</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12630; 16047</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>25726; 31279</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7194</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10972</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18166</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>43696</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>48988</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>92684</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>39897; 45628</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>41332; 52665</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>85908; 97060</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>33854</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>49706</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>83560</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>29159; 36730</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>45489; 52558</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>77084; 87756</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>51001</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60956</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>111957</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>44725; 55990</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>54713; 64953</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>103425; 118399</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>165575</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>207064</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>372638</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>154708; 173156</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>196854; 213829</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>358486; 383711</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP38E_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49,78; 100,0</t>
+          <t>38,0; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78,47; 100,0</t>
+          <t>82,17; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,03; 100,0</t>
+          <t>60,44; 100,0</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,4; 100,0</t>
+          <t>66,77; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,71; 100,0</t>
+          <t>79,83; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,25; 100,0</t>
+          <t>82,42; 98,12</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,57; 97,86</t>
+          <t>85,67; 97,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74,39; 94,79</t>
+          <t>76,18; 95,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,07; 94,99</t>
+          <t>83,32; 94,88</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,45; 92,52</t>
+          <t>74,22; 92,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82,08; 94,84</t>
+          <t>81,41; 94,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,04; 92,26</t>
+          <t>80,59; 92,32</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69,17; 86,59</t>
+          <t>68,96; 86,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,22; 94,05</t>
+          <t>79,95; 94,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77,34; 88,54</t>
+          <t>78,14; 88,55</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,22; 89,79</t>
+          <t>80,56; 89,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>85,98; 93,4</t>
+          <t>86,66; 93,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84,99; 90,97</t>
+          <t>84,84; 90,98</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9676; 19435</t>
+          <t>7386; 19435</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17173; 21885</t>
+          <t>17983; 21885</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26045; 41320</t>
+          <t>24973; 41320</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10114; 15232</t>
+          <t>10170; 15232</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12630; 16047</t>
+          <t>12811; 16047</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25726; 31279</t>
+          <t>25779; 30690</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39897; 45628</t>
+          <t>39944; 45545</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41332; 52665</t>
+          <t>42322; 52782</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85908; 97060</t>
+          <t>85140; 96953</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29159; 36730</t>
+          <t>29465; 36790</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45489; 52558</t>
+          <t>45114; 52564</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77084; 87756</t>
+          <t>76655; 87815</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44725; 55990</t>
+          <t>44591; 55847</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54713; 64953</t>
+          <t>55213; 64937</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>103425; 118399</t>
+          <t>104496; 118419</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>154708; 173156</t>
+          <t>155358; 173265</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>196854; 213829</t>
+          <t>198394; 214296</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>358486; 383711</t>
+          <t>357833; 383742</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP38E_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP38E_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,0; 100,0</t>
+          <t>74,15; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,17; 100,0</t>
+          <t>70,88; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,44; 100,0</t>
+          <t>82,13; 100,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,77; 100,0</t>
+          <t>82,11; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,83; 100,0</t>
+          <t>67,71; 100,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,42; 98,12</t>
+          <t>81,16; 98,47</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,67; 97,69</t>
+          <t>74,8; 94,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,18; 95,01</t>
+          <t>84,11; 97,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,32; 94,88</t>
+          <t>83,84; 95,03</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,22; 92,67</t>
+          <t>81,04; 95,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>81,41; 94,85</t>
+          <t>74,23; 93,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,59; 92,32</t>
+          <t>80,95; 92,62</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>68,96; 86,36</t>
+          <t>78,82; 93,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,95; 94,02</t>
+          <t>67,54; 86,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,14; 88,55</t>
+          <t>76,34; 88,26</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,56; 89,85</t>
+          <t>85,95; 93,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,66; 93,6</t>
+          <t>82,03; 90,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84,84; 90,98</t>
+          <t>85,41; 90,88</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20991</t>
+          <t>15887</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37157</t>
+          <t>35518</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7386; 19435</t>
+          <t>15303; 20637</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17983; 21885</t>
+          <t>11844; 16710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24973; 41320</t>
+          <t>30674; 37347</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15451</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29115</t>
+          <t>28464</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10170; 15232</t>
+          <t>12612; 15360</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12811; 16047</t>
+          <t>10316; 15237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25779; 30690</t>
+          <t>24833; 30128</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>17456</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>43696</t>
+          <t>43987</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>39542</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92684</t>
+          <t>83528</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39944; 45545</t>
+          <t>37461; 47208</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42322; 52782</t>
+          <t>35615; 41249</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85140; 96953</t>
+          <t>77493; 87833</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33854</t>
+          <t>45965</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49706</t>
+          <t>35584</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83560</t>
+          <t>81549</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29465; 36790</t>
+          <t>41495; 48658</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45114; 52564</t>
+          <t>30855; 38978</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76655; 87815</t>
+          <t>75095; 85923</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>72</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>51001</t>
+          <t>57403</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>60956</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111957</t>
+          <t>109292</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44591; 55847</t>
+          <t>51606; 61512</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>55213; 64937</t>
+          <t>44701; 56948</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104496; 118419</t>
+          <t>100504; 116197</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>243</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>165575</t>
+          <t>191758</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>207064</t>
+          <t>164048</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>372638</t>
+          <t>355806</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>155358; 173265</t>
+          <t>182780; 198552</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>198394; 214296</t>
+          <t>155517; 171856</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357833; 383742</t>
+          <t>343582; 365587</t>
         </is>
       </c>
     </row>
